--- a/data/trans_orig/P21D3_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D3_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir algún medicamento en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir algún medicamento en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62086</t>
+          <t>61157</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94413</t>
+          <t>94705</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45097</t>
+          <t>44721</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68534</t>
+          <t>68457</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>113159</t>
+          <t>115033</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>155002</t>
+          <t>156160</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,6%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>167353</t>
+          <t>168004</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>201407</t>
+          <t>202273</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>227583</t>
+          <t>228038</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>251621</t>
+          <t>252828</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>405116</t>
+          <t>403115</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>446296</t>
+          <t>444898</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,62%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>494</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,62 +1104,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4296</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>764</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4246</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49765</t>
+          <t>48921</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>227800</t>
+          <t>227049</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>79730</t>
+          <t>79743</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>112532</t>
+          <t>110036</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>111922</t>
+          <t>108399</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>309572</t>
+          <t>306318</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>426196</t>
+          <t>427681</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>608242</t>
+          <t>609320</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>324097</t>
+          <t>327157</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>357811</t>
+          <t>359061</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>781064</t>
+          <t>784826</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>988514</t>
+          <t>992753</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15684</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18276</t>
+          <t>18877</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -1638,97 +1638,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2960</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3816</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>767</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>3974</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>4889</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>4018</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36370</t>
+          <t>36531</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73010</t>
+          <t>72238</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38764</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69017</t>
+          <t>66652</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83609</t>
+          <t>82951</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129040</t>
+          <t>130109</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>255757</t>
+          <t>256951</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>292434</t>
+          <t>293128</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>259411</t>
+          <t>260158</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>288705</t>
+          <t>288320</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>525944</t>
+          <t>527147</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>572324</t>
+          <t>573511</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,87%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1673</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9438</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -2207,97 +2207,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1291</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1577</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>119196</t>
+          <t>116972</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>162614</t>
+          <t>162333</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>111971</t>
+          <t>114412</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>325222</t>
+          <t>297823</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>253057</t>
+          <t>250521</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>450940</t>
+          <t>465871</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>50,32%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244923</t>
+          <t>244918</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287457</t>
+          <t>290267</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>191773</t>
+          <t>218359</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>402919</t>
+          <t>400132</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>472675</t>
+          <t>456004</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>669697</t>
+          <t>671411</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,51%</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>406</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>545</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -2776,97 +2776,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1246</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1834</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4222</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>1246</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4243</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4247</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1246</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3900</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>243724</t>
+          <t>246203</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>490215</t>
+          <t>489607</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>307737</t>
+          <t>312466</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>562220</t>
+          <t>566321</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>623792</t>
+          <t>631918</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>945364</t>
+          <t>941522</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1164868</t>
+          <t>1165206</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1415592</t>
+          <t>1412086</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1010506</t>
+          <t>1011825</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1267577</t>
+          <t>1264713</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2292420</t>
+          <t>2297786</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2613632</t>
+          <t>2608184</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,06%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16110</t>
+          <t>14876</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22870</t>
+          <t>21991</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14827</t>
+          <t>14713</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32176</t>
+          <t>32824</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>558</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>614</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D3_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D3_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>77643</t>
+          <t>85957</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61157</t>
+          <t>67585</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94705</t>
+          <t>102886</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>56553</t>
+          <t>64469</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44721</t>
+          <t>52707</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68457</t>
+          <t>79392</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>134196</t>
+          <t>150427</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>115033</t>
+          <t>129615</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>156160</t>
+          <t>176968</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>185304</t>
+          <t>198530</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>168004</t>
+          <t>180967</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>202273</t>
+          <t>216520</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>240316</t>
+          <t>257178</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>228038</t>
+          <t>242192</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>252828</t>
+          <t>268790</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>425620</t>
+          <t>455708</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>403115</t>
+          <t>430529</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>444898</t>
+          <t>477177</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>77,93%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>526</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,22 +1021,22 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>11315</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>299287</t>
+          <t>324160</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>299287</t>
+          <t>324160</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>299287</t>
+          <t>324160</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>565886</t>
+          <t>612283</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>565886</t>
+          <t>612283</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>565886</t>
+          <t>612283</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>136530</t>
+          <t>167411</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48921</t>
+          <t>145812</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>227049</t>
+          <t>192349</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>94803</t>
+          <t>105546</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>79743</t>
+          <t>87462</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>110036</t>
+          <t>122185</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>231332</t>
+          <t>272957</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>108399</t>
+          <t>244189</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>306318</t>
+          <t>305351</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>519810</t>
+          <t>300647</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>427681</t>
+          <t>275581</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>609320</t>
+          <t>321907</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>343164</t>
+          <t>387742</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>327157</t>
+          <t>371241</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>359061</t>
+          <t>406668</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>862975</t>
+          <t>688389</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>784826</t>
+          <t>658259</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>992753</t>
+          <t>716875</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>73,63%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>15979</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>19438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>3819</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>503394</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>503394</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>503394</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>973601</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>973601</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>973601</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>51891</t>
+          <t>63272</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36531</t>
+          <t>45182</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72238</t>
+          <t>86124</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>51321</t>
+          <t>55010</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>43390</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66652</t>
+          <t>71951</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>103212</t>
+          <t>118282</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82951</t>
+          <t>95306</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>130109</t>
+          <t>142634</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>277090</t>
+          <t>311331</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>256951</t>
+          <t>288501</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>293128</t>
+          <t>329487</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>275756</t>
+          <t>321079</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>260158</t>
+          <t>304082</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>288320</t>
+          <t>332984</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>552845</t>
+          <t>632409</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>527147</t>
+          <t>608789</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>573511</t>
+          <t>655511</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,8%</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>9139</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>378649</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>378649</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>378649</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>755232</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>755232</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>755232</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>138993</t>
+          <t>156446</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>116972</t>
+          <t>135935</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>162333</t>
+          <t>179242</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>172447</t>
+          <t>119392</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>114412</t>
+          <t>102396</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>297823</t>
+          <t>137712</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>311439</t>
+          <t>275837</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>250521</t>
+          <t>245752</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>465871</t>
+          <t>305716</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>268252</t>
+          <t>276193</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244918</t>
+          <t>253228</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>290267</t>
+          <t>296459</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>342610</t>
+          <t>368326</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>218359</t>
+          <t>350071</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>400132</t>
+          <t>385530</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>610863</t>
+          <t>644519</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>456004</t>
+          <t>615472</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>671411</t>
+          <t>675421</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>73,09%</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>721</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>430</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2473</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>517942</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>517942</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>517942</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>925895</t>
+          <t>924093</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>925895</t>
+          <t>924093</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>925895</t>
+          <t>924093</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>405056</t>
+          <t>473086</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>246203</t>
+          <t>429964</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>489607</t>
+          <t>518785</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>375123</t>
+          <t>344416</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>312466</t>
+          <t>312930</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>566321</t>
+          <t>375775</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>780179</t>
+          <t>817503</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>631918</t>
+          <t>766603</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>941522</t>
+          <t>869858</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1250455</t>
+          <t>1086701</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1165206</t>
+          <t>1041293</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1412086</t>
+          <t>1129936</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1201847</t>
+          <t>1334324</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1011825</t>
+          <t>1302634</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1264713</t>
+          <t>1366730</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2452303</t>
+          <t>2421025</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2297786</t>
+          <t>2367854</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2608184</t>
+          <t>2473655</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>75,76%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14876</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>16183</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21991</t>
+          <t>25321</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>22492</t>
+          <t>23923</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14713</t>
+          <t>16527</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32824</t>
+          <t>34179</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,17 +3380,17 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,22 +3410,22 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>705</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
